--- a/Solar_modules_and_cells.xlsx
+++ b/Solar_modules_and_cells.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Solar Module Sold (MW)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Solar Cell Sold (MW)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solar Module Sold (MW)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solar Cell Sold (MW)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </externalReferences>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -420,14 +420,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -461,25 +461,25 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr b="1"/>
                 </a:pPr>
@@ -592,7 +592,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln w="3175">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3175">
       <a:solidFill>
         <a:schemeClr val="accent1"/>
       </a:solidFill>
@@ -603,14 +603,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -644,25 +644,25 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr b="1"/>
                 </a:pPr>
@@ -763,7 +763,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln w="3175">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3175">
       <a:solidFill>
         <a:schemeClr val="accent1"/>
       </a:solidFill>
@@ -774,14 +774,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -815,25 +815,25 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr b="1"/>
                 </a:pPr>
@@ -946,7 +946,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln w="3175">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3175">
       <a:solidFill>
         <a:schemeClr val="accent1"/>
       </a:solidFill>
@@ -957,13 +957,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
               <a:t>None</a:t>
             </a:r>
@@ -993,25 +993,25 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr b="1"/>
                 </a:pPr>
@@ -1112,7 +1112,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln w="3175">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3175">
       <a:solidFill>
         <a:schemeClr val="accent1"/>
       </a:solidFill>
@@ -1174,12 +1174,6 @@
     <author>Dheeraj Kripalani</author>
   </authors>
   <commentList>
-    <comment ref="A27" authorId="0" shapeId="0">
-      <text>
-        <t>Dheeraj Kripalani:
-Tata Power Renewable Energy Limited + TP Solar Limited</t>
-      </text>
-    </comment>
     <comment ref="A28" authorId="0" shapeId="0">
       <text>
         <t>Dheeraj Kripalani:
@@ -1215,7 +1209,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>10</col>
@@ -1235,9 +1229,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1262,9 +1256,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1274,7 +1268,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>6</col>
@@ -1294,9 +1288,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1321,9 +1315,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1333,8 +1327,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Data"/>
       <sheetName val="India - Installed Capacity"/>
@@ -1777,7 +1771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:T120"/>
+  <dimension ref="A2:V120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1819,7 +1813,9 @@
       <c r="Q2" s="35" t="n"/>
       <c r="R2" s="35" t="n"/>
       <c r="S2" s="35" t="n"/>
-      <c r="T2" s="36" t="n"/>
+      <c r="T2" s="35" t="n"/>
+      <c r="U2" s="35" t="n"/>
+      <c r="V2" s="36" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="37" t="n"/>
@@ -1918,6 +1914,16 @@
           <t>Jul</t>
         </is>
       </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1977,10 +1983,16 @@
         <v>0.88</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>1.78</v>
       </c>
     </row>
     <row r="5">
@@ -2044,7 +2056,13 @@
         <v>6.16</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>5.04</v>
+        <v>5.16</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="6">
@@ -2060,7 +2078,7 @@
         <v>21.67</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>20.71</v>
+        <v>19.47</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>6.31</v>
@@ -2087,7 +2105,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.66</v>
+        <v>13.65</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>24.9</v>
@@ -2110,6 +2128,12 @@
       <c r="T6" s="4" t="n">
         <v>21.59</v>
       </c>
+      <c r="U6" s="4" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>12.33</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2174,6 +2198,12 @@
       <c r="T7" s="4" t="n">
         <v>0.12</v>
       </c>
+      <c r="U7" s="4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2224,19 +2254,25 @@
         <v>8.970000000000001</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>10.06</v>
+        <v>9.34</v>
       </c>
       <c r="Q8" s="4" t="n">
         <v>1.37</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>10.18</v>
+        <v>17.16</v>
       </c>
       <c r="S8" s="4" t="n">
         <v>1.05</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>6.03</v>
+        <v>7.21</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="9">
@@ -2294,13 +2330,19 @@
         <v>43.76</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>44.72</v>
+        <v>45.05</v>
       </c>
       <c r="S9" s="4" t="n">
         <v>60.77</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>56.51</v>
+        <v>56.94</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>63.52</v>
       </c>
     </row>
     <row r="10">
@@ -2352,19 +2394,25 @@
         <v>1.98</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>4.93</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>5.56</v>
+        <v>5.55</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3.39</v>
+        <v>4.29</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>3.02</v>
       </c>
     </row>
     <row r="11">
@@ -2377,7 +2425,7 @@
         <v>12.36</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>12.31</v>
+        <v>12.32</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>14</v>
@@ -2389,13 +2437,13 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6.37</v>
+        <v>6.61</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>5.74</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.23</v>
+        <v>4.39</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>7.52</v>
@@ -2407,10 +2455,10 @@
         <v>12.52</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>10.76</v>
+        <v>11.37</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>10.28</v>
@@ -2422,13 +2470,19 @@
         <v>9.17</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>16.18</v>
+        <v>16.43</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>24.02</v>
+        <v>24.04</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>22.13</v>
+        <v>23.94</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>12.6</v>
       </c>
     </row>
     <row r="12">
@@ -2480,7 +2534,7 @@
         <v>0.24</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="Q12" s="4" t="n">
         <v>0.12</v>
@@ -2492,7 +2546,13 @@
         <v>0.62</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="13">
@@ -2550,7 +2610,7 @@
         <v>5.24</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>9.59</v>
+        <v>9.6</v>
       </c>
       <c r="S13" s="4" t="n">
         <v>5.74</v>
@@ -2558,6 +2618,12 @@
       <c r="T13" s="4" t="n">
         <v>8.460000000000001</v>
       </c>
+      <c r="U13" s="4" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>7.26</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2608,7 +2674,7 @@
         <v>0.31</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q14" s="4" t="n">
         <v>0</v>
@@ -2617,10 +2683,16 @@
         <v>0.25</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="15">
@@ -2672,10 +2744,10 @@
         <v>0.46</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="R15" s="4" t="n">
         <v>0.44</v>
@@ -2686,6 +2758,12 @@
       <c r="T15" s="4" t="n">
         <v>0.44</v>
       </c>
+      <c r="U15" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2748,7 +2826,13 @@
         <v>30.43</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>31.71</v>
+        <v>45.6</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>5.64</v>
       </c>
     </row>
     <row r="17">
@@ -2794,7 +2878,7 @@
         <v>1.11</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="O17" s="4" t="n">
         <v>1.35</v>
@@ -2812,7 +2896,13 @@
         <v>2.91</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="18">
@@ -2825,7 +2915,7 @@
         <v>3.78</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>7.87</v>
@@ -2870,13 +2960,19 @@
         <v>1.78</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.65</v>
+        <v>4.07</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.88</v>
+        <v>3.32</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>3.15</v>
       </c>
     </row>
     <row r="19">
@@ -2940,7 +3036,13 @@
         <v>0</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>21.27</v>
+        <v>21.32</v>
+      </c>
+      <c r="U19" s="4" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>34.72</v>
       </c>
     </row>
     <row r="20">
@@ -3004,7 +3106,13 @@
         <v>121.9</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>52.36</v>
+        <v>61.65</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>64.56</v>
       </c>
     </row>
     <row r="21">
@@ -3056,19 +3164,25 @@
         <v>182.66</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>323.05</v>
+        <v>335.06</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>25.25</v>
+        <v>47.88</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>18.13</v>
+        <v>18.39</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>8.640000000000001</v>
+        <v>39.57</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>46.57</v>
+        <v>59.91</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>26.65</v>
       </c>
     </row>
     <row r="22">
@@ -3111,7 +3225,7 @@
         <v>22.5</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>38.55</v>
+        <v>38.57</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>43.84</v>
@@ -3120,19 +3234,25 @@
         <v>45.56</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>54.95</v>
+        <v>54.96</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>49.07</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>73.72</v>
+        <v>73.7</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>90.83</v>
+        <v>90.84</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>74.95999999999999</v>
+        <v>78.16</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>75.3</v>
       </c>
     </row>
     <row r="23">
@@ -3163,25 +3283,25 @@
         <v>0.11</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.39</v>
+        <v>0.78</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.19</v>
+        <v>2.19</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>8.18</v>
@@ -3196,7 +3316,13 @@
         <v>12.32</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>17.94</v>
+        <v>18.65</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>3.88</v>
       </c>
     </row>
     <row r="24">
@@ -3230,7 +3356,7 @@
         <v>10.11</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>19.69</v>
+        <v>22.31</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>12.76</v>
@@ -3245,22 +3371,28 @@
         <v>6.16</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.92</v>
+        <v>4.12</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.16</v>
+        <v>4.83</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>5.78</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>8.1</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>22.89</v>
+        <v>23.69</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>10.33</v>
+        <v>15.82</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>6.23</v>
       </c>
     </row>
     <row r="25">
@@ -3300,7 +3432,7 @@
         <v>4.87</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="M25" s="4" t="n">
         <v>2.46</v>
@@ -3309,22 +3441,28 @@
         <v>0.71</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.79</v>
+        <v>0.37</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>14.59</v>
+        <v>15</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="26">
@@ -3379,16 +3517,22 @@
         <v>4.79</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.59</v>
+        <v>5.6</v>
       </c>
       <c r="R26" s="4" t="n">
         <v>16.78</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>9.17</v>
+        <v>13.25</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>7.65</v>
+        <v>18.18</v>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>2.95</v>
       </c>
     </row>
     <row r="27">
@@ -3428,7 +3572,7 @@
         <v>1.51</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="M27" s="4" t="n">
         <v>5.47</v>
@@ -3440,19 +3584,25 @@
         <v>3.65</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.91</v>
+        <v>5.82</v>
       </c>
       <c r="Q27" s="4" t="n">
         <v>1.17</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>5.88</v>
+        <v>5.9</v>
       </c>
       <c r="S27" s="4" t="n">
         <v>7.07</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>7.73</v>
+        <v>8.31</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>3.88</v>
       </c>
     </row>
     <row r="28">
@@ -3516,7 +3666,13 @@
         <v>13.25</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>13.35</v>
+        <v>14.03</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -3559,7 +3715,7 @@
         <v>19.35</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>26.65</v>
+        <v>22.4</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>30.64</v>
@@ -3577,10 +3733,16 @@
         <v>33.03</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>31.7</v>
+        <v>31.74</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>42.85</v>
+        <v>44.13</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>34.38</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>35.26</v>
       </c>
     </row>
     <row r="30">
@@ -3641,10 +3803,16 @@
         <v>47.71</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>54.41</v>
+        <v>55.28</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>29.71</v>
+        <v>37.9</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>37.43</v>
       </c>
     </row>
     <row r="31">
@@ -3708,7 +3876,13 @@
         <v>13.32</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>12.41</v>
+        <v>13.73</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>10.27</v>
       </c>
     </row>
     <row r="32">
@@ -3751,7 +3925,7 @@
         <v>0.91</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>0.44</v>
@@ -3760,19 +3934,25 @@
         <v>0.5</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="Q32" s="4" t="n">
         <v>0.28</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="33">
@@ -3838,6 +4018,12 @@
       <c r="T33" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="U33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -3882,25 +4068,31 @@
         <v>5.95</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.05</v>
+        <v>5.04</v>
       </c>
       <c r="O34" s="4" t="n">
         <v>2.94</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>13.5</v>
+        <v>13.73</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>10.73</v>
+        <v>12.95</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>3.09</v>
+        <v>6.04</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>3.51</v>
+        <v>3.61</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>4.19</v>
+        <v>6.85</v>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="35">
@@ -3961,10 +4153,16 @@
         <v>1.72</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>4.95</v>
       </c>
     </row>
     <row r="36">
@@ -4010,7 +4208,7 @@
         <v>3.8</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="O36" s="4" t="n">
         <v>0</v>
@@ -4030,6 +4228,12 @@
       <c r="T36" s="4" t="n">
         <v>12.1</v>
       </c>
+      <c r="U36" s="4" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>6.01</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -4044,7 +4248,7 @@
         <v>0.08</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>0.31</v>
@@ -4053,25 +4257,25 @@
         <v>0.52</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>0.25</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>0.49</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>1.92</v>
@@ -4080,19 +4284,25 @@
         <v>1.21</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>45.77</v>
+        <v>50.77</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>0.66</v>
+        <v>2.41</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>6.02</v>
+        <v>9.02</v>
       </c>
       <c r="T37" s="4" t="n">
-        <v>5.62</v>
+        <v>9.6</v>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -4158,6 +4368,12 @@
       <c r="T38" s="4" t="n">
         <v>2.05</v>
       </c>
+      <c r="U38" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>5.16</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -4205,7 +4421,7 @@
         <v>4.29</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>4.25</v>
@@ -4214,13 +4430,19 @@
         <v>6.59</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>19.14</v>
+        <v>19.16</v>
       </c>
       <c r="S39" s="4" t="n">
         <v>15.74</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>14.38</v>
+        <v>14.42</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>10.13</v>
       </c>
     </row>
     <row r="40">
@@ -4281,10 +4503,16 @@
         <v>53.2</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>79.66</v>
+        <v>79.64</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>35.95</v>
+        <v>36.25</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>33.49</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>34.59</v>
       </c>
     </row>
     <row r="41">
@@ -4309,13 +4537,13 @@
         <v>128.45</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>133.41</v>
+        <v>133.4</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>138.63</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>139.86</v>
+        <v>139.85</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>127.89</v>
@@ -4336,7 +4564,7 @@
         <v>130.54</v>
       </c>
       <c r="P41" s="4" t="n">
-        <v>178.68</v>
+        <v>178.67</v>
       </c>
       <c r="Q41" s="4" t="n">
         <v>161.71</v>
@@ -4348,7 +4576,13 @@
         <v>174.05</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>120.08</v>
+        <v>163.53</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>161.22</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>133.97</v>
       </c>
     </row>
     <row r="42">
@@ -4382,7 +4616,7 @@
         <v>89.17</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>42.89</v>
+        <v>42.88</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>100.19</v>
@@ -4409,10 +4643,16 @@
         <v>183.92</v>
       </c>
       <c r="S42" s="4" t="n">
-        <v>149.54</v>
+        <v>149.53</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>99.20999999999999</v>
+        <v>141.63</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>154.4</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>117.75</v>
       </c>
     </row>
     <row r="43">
@@ -4470,13 +4710,19 @@
         <v>2.33</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>6.08</v>
+        <v>6.14</v>
       </c>
       <c r="S43" s="4" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>5.12</v>
+        <v>7.36</v>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="V43" s="4" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="44">
@@ -4540,6 +4786,12 @@
         <v>0.23</v>
       </c>
       <c r="T44" s="4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V44" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4556,7 +4808,7 @@
         <v>5.77</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>4.96</v>
+        <v>4.98</v>
       </c>
       <c r="E45" s="4" t="n">
         <v>3.44</v>
@@ -4604,7 +4856,13 @@
         <v>11.48</v>
       </c>
       <c r="T45" s="4" t="n">
-        <v>7.75</v>
+        <v>9.66</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>7.55</v>
       </c>
     </row>
     <row r="46">
@@ -4614,13 +4872,13 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>16.73</v>
+        <v>16.19</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>14.61</v>
+        <v>13.37</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>21.91</v>
+        <v>21.88</v>
       </c>
       <c r="E46" s="4" t="n">
         <v>15.25</v>
@@ -4656,10 +4914,10 @@
         <v>28.53</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>31.77</v>
+        <v>29.45</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>25.59</v>
+        <v>25.62</v>
       </c>
       <c r="R46" s="4" t="n">
         <v>31.3</v>
@@ -4668,7 +4926,13 @@
         <v>33.83</v>
       </c>
       <c r="T46" s="4" t="n">
-        <v>20.91</v>
+        <v>27.2</v>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="V46" s="4" t="n">
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4684,7 +4948,7 @@
         <v>6.88</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>4.87</v>
+        <v>4.85</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>6.01</v>
@@ -4732,7 +4996,13 @@
         <v>9.51</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>7.5</v>
+        <v>7.68</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="48">
@@ -4798,6 +5068,12 @@
       <c r="T48" s="4" t="n">
         <v>0.48</v>
       </c>
+      <c r="U48" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>1.46</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -4857,10 +5133,16 @@
         <v>2.24</v>
       </c>
       <c r="S49" s="4" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>0.98</v>
+        <v>1.66</v>
+      </c>
+      <c r="U49" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V49" s="4" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="50">
@@ -4921,10 +5203,16 @@
         <v>82.75</v>
       </c>
       <c r="S50" s="4" t="n">
-        <v>86.54000000000001</v>
+        <v>86.87</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>102.33</v>
+        <v>103.71</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>71.23999999999999</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -4970,7 +5258,7 @@
         <v>40.33</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="O51" s="4" t="n">
         <v>71.84999999999999</v>
@@ -4988,7 +5276,13 @@
         <v>174.51</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>96.03</v>
+        <v>100.9</v>
+      </c>
+      <c r="U51" s="4" t="n">
+        <v>150.74</v>
+      </c>
+      <c r="V51" s="4" t="n">
+        <v>130.37</v>
       </c>
     </row>
     <row r="52">
@@ -5052,7 +5346,13 @@
         <v>5.02</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>4.4</v>
+        <v>4.59</v>
+      </c>
+      <c r="U52" s="4" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>4.18</v>
       </c>
     </row>
     <row r="53">
@@ -5118,6 +5418,12 @@
       <c r="T53" s="4" t="n">
         <v>1.75</v>
       </c>
+      <c r="U53" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V53" s="4" t="n">
+        <v>1.49</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -5171,16 +5477,22 @@
         <v>24.95</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>25.76</v>
+        <v>25.79</v>
       </c>
       <c r="R54" s="4" t="n">
-        <v>43.21</v>
+        <v>43.04</v>
       </c>
       <c r="S54" s="4" t="n">
         <v>63.9</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>55.03</v>
+        <v>55.14</v>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>44.93</v>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>37.43</v>
       </c>
     </row>
     <row r="55">
@@ -5244,7 +5556,13 @@
         <v>15.33</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>19.44</v>
+        <v>19.76</v>
+      </c>
+      <c r="U55" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="V55" s="4" t="n">
+        <v>11.04</v>
       </c>
     </row>
     <row r="56">
@@ -5290,7 +5608,7 @@
         <v>24.11</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>55.75</v>
+        <v>56.14</v>
       </c>
       <c r="O56" s="4" t="n">
         <v>66.86</v>
@@ -5302,13 +5620,19 @@
         <v>59</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>137.53</v>
+        <v>140.68</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>113.88</v>
+        <v>119.61</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>77.51000000000001</v>
+        <v>84.98</v>
+      </c>
+      <c r="U56" s="4" t="n">
+        <v>110.16</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>115.66</v>
       </c>
     </row>
     <row r="57">
@@ -5372,7 +5696,13 @@
         <v>10.96</v>
       </c>
       <c r="T57" s="4" t="n">
-        <v>3.34</v>
+        <v>6.19</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="V57" s="4" t="n">
+        <v>7.9</v>
       </c>
     </row>
     <row r="58">
@@ -5400,7 +5730,7 @@
         <v>3.97</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>5.29</v>
@@ -5409,7 +5739,7 @@
         <v>1.83</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="L58" s="4" t="n">
         <v>1.77</v>
@@ -5436,7 +5766,13 @@
         <v>3.71</v>
       </c>
       <c r="T58" s="4" t="n">
-        <v>4.48</v>
+        <v>4.49</v>
+      </c>
+      <c r="U58" s="4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>4.01</v>
       </c>
     </row>
     <row r="59">
@@ -5485,22 +5821,28 @@
         <v>2.03</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>1.37</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="R59" s="4" t="n">
         <v>0.02</v>
       </c>
       <c r="S59" s="4" t="n">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="T59" s="4" t="n">
-        <v>4.95</v>
+        <v>5.82</v>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="60">
@@ -5561,10 +5903,16 @@
         <v>8.470000000000001</v>
       </c>
       <c r="S60" s="4" t="n">
-        <v>6.67</v>
+        <v>6.72</v>
       </c>
       <c r="T60" s="4" t="n">
-        <v>2.13</v>
+        <v>4.01</v>
+      </c>
+      <c r="U60" s="4" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="61">
@@ -5630,6 +5978,12 @@
       <c r="T61" s="4" t="n">
         <v>0.38</v>
       </c>
+      <c r="U61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -5694,6 +6048,12 @@
       <c r="T62" s="4" t="n">
         <v>3.87</v>
       </c>
+      <c r="U62" s="4" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="V62" s="4" t="n">
+        <v>1.68</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -5702,25 +6062,25 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>1.02</v>
+        <v>0.74</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>2.43</v>
+        <v>1.18</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="I63" s="4" t="n">
         <v>1.22</v>
@@ -5735,10 +6095,10 @@
         <v>0.42</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>3.16</v>
+        <v>2.97</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>3.12</v>
+        <v>2.97</v>
       </c>
       <c r="O63" s="4" t="n">
         <v>2.96</v>
@@ -5747,7 +6107,7 @@
         <v>2.04</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="R63" s="4" t="n">
         <v>2.14</v>
@@ -5756,7 +6116,13 @@
         <v>3.3</v>
       </c>
       <c r="T63" s="4" t="n">
-        <v>4.2</v>
+        <v>5.37</v>
+      </c>
+      <c r="U63" s="4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="V63" s="4" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="64">
@@ -5822,6 +6188,12 @@
       <c r="T64" s="4" t="n">
         <v>4.79</v>
       </c>
+      <c r="U64" s="4" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="V64" s="4" t="n">
+        <v>3.31</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -5872,19 +6244,25 @@
         <v>12.52</v>
       </c>
       <c r="P65" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>12.36</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>1.38</v>
+        <v>5.69</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>15.32</v>
+        <v>17.35</v>
       </c>
       <c r="S65" s="4" t="n">
-        <v>7.44</v>
+        <v>8.51</v>
       </c>
       <c r="T65" s="4" t="n">
-        <v>3.83</v>
+        <v>5.77</v>
+      </c>
+      <c r="U65" s="4" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="V65" s="4" t="n">
+        <v>7.99</v>
       </c>
     </row>
     <row r="66">
@@ -5903,7 +6281,7 @@
         <v>5.16</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="F66" s="4" t="n">
         <v>2.95</v>
@@ -5948,7 +6326,13 @@
         <v>3.6</v>
       </c>
       <c r="T66" s="4" t="n">
-        <v>3.33</v>
+        <v>3.79</v>
+      </c>
+      <c r="U66" s="4" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="V66" s="4" t="n">
+        <v>4.48</v>
       </c>
     </row>
     <row r="67">
@@ -5958,16 +6342,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>0.39</v>
+        <v>0.7</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>3.41</v>
+        <v>3.66</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="F67" s="4" t="n">
         <v>1.82</v>
@@ -5976,19 +6360,19 @@
         <v>0.54</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M67" s="4" t="n">
         <v>1.12</v>
@@ -5997,22 +6381,28 @@
         <v>0.8</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>2.31</v>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="R67" s="4" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T67" s="4" t="n">
-        <v>0.27</v>
+        <v>1</v>
+      </c>
+      <c r="U67" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V67" s="4" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -6022,61 +6412,67 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
-        <v>143.53</v>
+        <v>143.38</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>138</v>
+        <v>137.84</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>240.98</v>
+        <v>240.67</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>183.11</v>
+        <v>183</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>217.94</v>
+        <v>217.79</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>239.29</v>
+        <v>238.41</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>256.3</v>
+        <v>256.31</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>267.62</v>
+        <v>267.24</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>557.0599999999999</v>
+        <v>556.62</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>251.78</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>270.65</v>
+        <v>270.29</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>169.92</v>
+        <v>169.47</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>88.15000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>96.18000000000001</v>
+        <v>96.17</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>121.19</v>
+        <v>120.79</v>
       </c>
       <c r="Q68" s="4" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>123.92</v>
+        <v>123.93</v>
       </c>
       <c r="S68" s="4" t="n">
-        <v>158.94</v>
+        <v>158.15</v>
       </c>
       <c r="T68" s="4" t="n">
-        <v>152.82</v>
+        <v>152.14</v>
+      </c>
+      <c r="U68" s="4" t="n">
+        <v>124.95</v>
+      </c>
+      <c r="V68" s="4" t="n">
+        <v>135.42</v>
       </c>
     </row>
     <row r="69">
@@ -6142,6 +6538,12 @@
       <c r="T69" s="4" t="n">
         <v>1.62</v>
       </c>
+      <c r="U69" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="V69" s="4" t="n">
+        <v>146.63</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -6198,13 +6600,19 @@
         <v>3.17</v>
       </c>
       <c r="R70" s="4" t="n">
-        <v>4.56</v>
+        <v>4.65</v>
       </c>
       <c r="S70" s="4" t="n">
-        <v>8.59</v>
+        <v>8.76</v>
       </c>
       <c r="T70" s="4" t="n">
-        <v>11.13</v>
+        <v>11.98</v>
+      </c>
+      <c r="U70" s="4" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="V70" s="4" t="n">
+        <v>12.39</v>
       </c>
     </row>
     <row r="71">
@@ -6268,7 +6676,13 @@
         <v>2.21</v>
       </c>
       <c r="T71" s="4" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
+      </c>
+      <c r="U71" s="4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V71" s="4" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="72">
@@ -6332,7 +6746,13 @@
         <v>50.75</v>
       </c>
       <c r="T72" s="4" t="n">
-        <v>22.06</v>
+        <v>22.08</v>
+      </c>
+      <c r="U72" s="4" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="V72" s="4" t="n">
+        <v>36.28</v>
       </c>
     </row>
     <row r="73">
@@ -6378,25 +6798,31 @@
         <v>204.31</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>278.54</v>
+        <v>278.55</v>
       </c>
       <c r="O73" s="4" t="n">
         <v>268.08</v>
       </c>
       <c r="P73" s="4" t="n">
-        <v>245.68</v>
+        <v>245.69</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>229.77</v>
+        <v>229.78</v>
       </c>
       <c r="R73" s="4" t="n">
-        <v>281.29</v>
+        <v>281.31</v>
       </c>
       <c r="S73" s="4" t="n">
-        <v>484.5</v>
+        <v>484.64</v>
       </c>
       <c r="T73" s="4" t="n">
-        <v>385.45</v>
+        <v>454.62</v>
+      </c>
+      <c r="U73" s="4" t="n">
+        <v>405.53</v>
+      </c>
+      <c r="V73" s="4" t="n">
+        <v>440.35</v>
       </c>
     </row>
     <row r="74">
@@ -6457,10 +6883,16 @@
         <v>35.11</v>
       </c>
       <c r="S74" s="4" t="n">
-        <v>28.46</v>
+        <v>26.09</v>
       </c>
       <c r="T74" s="4" t="n">
-        <v>5.35</v>
+        <v>5.33</v>
+      </c>
+      <c r="U74" s="4" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>36.92</v>
       </c>
     </row>
     <row r="75">
@@ -6470,61 +6902,67 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>6.65</v>
+        <v>6.73</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>16.8</v>
+        <v>17.06</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>13.61</v>
+        <v>13.84</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>9.26</v>
+        <v>9.51</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>12.23</v>
+        <v>12.38</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>19.74</v>
+        <v>18.43</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>18.8</v>
+        <v>18.96</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14.16</v>
+        <v>14.37</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>40.1</v>
+        <v>40.19</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>12.74</v>
+        <v>12.93</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>12.61</v>
+        <v>13.55</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>22.85</v>
+        <v>23.57</v>
       </c>
       <c r="N75" s="4" t="n">
-        <v>22.92</v>
+        <v>29.63</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>27.53</v>
+        <v>32.64</v>
       </c>
       <c r="P75" s="4" t="n">
-        <v>37.49</v>
+        <v>42.23</v>
       </c>
       <c r="Q75" s="4" t="n">
-        <v>16.18</v>
+        <v>19.08</v>
       </c>
       <c r="R75" s="4" t="n">
-        <v>34.49</v>
+        <v>55.17</v>
       </c>
       <c r="S75" s="4" t="n">
-        <v>65.69</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="T75" s="4" t="n">
-        <v>56.06</v>
+        <v>72.18000000000001</v>
+      </c>
+      <c r="U75" s="4" t="n">
+        <v>94.19</v>
+      </c>
+      <c r="V75" s="4" t="n">
+        <v>108.07</v>
       </c>
     </row>
     <row r="76">
@@ -6607,6 +7045,14 @@
       </c>
       <c r="T76" s="6">
         <f>SUM(T4:T75)</f>
+        <v/>
+      </c>
+      <c r="U76" s="6">
+        <f>SUM(U4:U75)</f>
+        <v/>
+      </c>
+      <c r="V76" s="6">
+        <f>SUM(V4:V75)</f>
         <v/>
       </c>
     </row>
@@ -6649,7 +7095,9 @@
       <c r="Q79" s="35" t="n"/>
       <c r="R79" s="35" t="n"/>
       <c r="S79" s="35" t="n"/>
-      <c r="T79" s="36" t="n"/>
+      <c r="T79" s="35" t="n"/>
+      <c r="U79" s="35" t="n"/>
+      <c r="V79" s="36" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="37" t="n"/>
@@ -6748,6 +7196,16 @@
           <t>Jul</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
@@ -6831,6 +7289,14 @@
         <f>T68+T69</f>
         <v/>
       </c>
+      <c r="U81">
+        <f>U68+U69</f>
+        <v/>
+      </c>
+      <c r="V81">
+        <f>V68+V69</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -6914,6 +7380,14 @@
         <f>T41+T42</f>
         <v/>
       </c>
+      <c r="U82">
+        <f>U41+U42</f>
+        <v/>
+      </c>
+      <c r="V82">
+        <f>V41+V42</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -6997,6 +7471,14 @@
         <f>T21</f>
         <v/>
       </c>
+      <c r="U83">
+        <f>U21</f>
+        <v/>
+      </c>
+      <c r="V83">
+        <f>V21</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
@@ -7080,6 +7562,14 @@
         <f>T73</f>
         <v/>
       </c>
+      <c r="U84">
+        <f>U73</f>
+        <v/>
+      </c>
+      <c r="V84">
+        <f>V73</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -7163,6 +7653,14 @@
         <f>T50+T51</f>
         <v/>
       </c>
+      <c r="U85">
+        <f>U50+U51</f>
+        <v/>
+      </c>
+      <c r="V85">
+        <f>V50+V51</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
@@ -7246,6 +7744,14 @@
         <f>T19+T20</f>
         <v/>
       </c>
+      <c r="U86">
+        <f>U19+U20</f>
+        <v/>
+      </c>
+      <c r="V86">
+        <f>V19+V20</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -7329,6 +7835,14 @@
         <f>T56</f>
         <v/>
       </c>
+      <c r="U87">
+        <f>U56</f>
+        <v/>
+      </c>
+      <c r="V87">
+        <f>V56</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -7412,6 +7926,14 @@
         <f>T9</f>
         <v/>
       </c>
+      <c r="U88">
+        <f>U9</f>
+        <v/>
+      </c>
+      <c r="V88">
+        <f>V9</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
@@ -7495,6 +8017,14 @@
         <f>T22</f>
         <v/>
       </c>
+      <c r="U89">
+        <f>U22</f>
+        <v/>
+      </c>
+      <c r="V89">
+        <f>V22</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -7578,6 +8108,14 @@
         <f>T54</f>
         <v/>
       </c>
+      <c r="U90">
+        <f>U54</f>
+        <v/>
+      </c>
+      <c r="V90">
+        <f>V54</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -7661,6 +8199,14 @@
         <f>T25+T26</f>
         <v/>
       </c>
+      <c r="U91">
+        <f>U25+U26</f>
+        <v/>
+      </c>
+      <c r="V91">
+        <f>V25+V26</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
@@ -7744,6 +8290,14 @@
         <f>T72</f>
         <v/>
       </c>
+      <c r="U92">
+        <f>U72</f>
+        <v/>
+      </c>
+      <c r="V92">
+        <f>V72</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -7827,6 +8381,14 @@
         <f>T59+T60</f>
         <v/>
       </c>
+      <c r="U93">
+        <f>U59+U60</f>
+        <v/>
+      </c>
+      <c r="V93">
+        <f>V59+V60</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
@@ -7910,6 +8472,14 @@
         <f>+T95-SUM(T81:T93)</f>
         <v/>
       </c>
+      <c r="U94">
+        <f>+U95-SUM(U81:U93)</f>
+        <v/>
+      </c>
+      <c r="V94">
+        <f>+V95-SUM(V81:V93)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
@@ -7991,6 +8561,14 @@
       </c>
       <c r="T95" s="13">
         <f>+T76</f>
+        <v/>
+      </c>
+      <c r="U95">
+        <f>+U76</f>
+        <v/>
+      </c>
+      <c r="V95">
+        <f>+V76</f>
         <v/>
       </c>
     </row>
@@ -8565,10 +9143,10 @@
   <mergeCells count="6">
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="A79:A80"/>
-    <mergeCell ref="N79:T79"/>
+    <mergeCell ref="N2:V2"/>
+    <mergeCell ref="N79:V79"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B79:M79"/>
-    <mergeCell ref="N2:T2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8582,7 +9160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:T59"/>
+  <dimension ref="A3:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47.140625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8624,7 +9202,9 @@
       <c r="Q3" s="35" t="n"/>
       <c r="R3" s="35" t="n"/>
       <c r="S3" s="35" t="n"/>
-      <c r="T3" s="36" t="n"/>
+      <c r="T3" s="35" t="n"/>
+      <c r="U3" s="35" t="n"/>
+      <c r="V3" s="36" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="37" t="n"/>
@@ -8723,6 +9303,16 @@
           <t>Jul</t>
         </is>
       </c>
+      <c r="U4" s="26" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="V4" s="26" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -8787,6 +9377,12 @@
       <c r="T5" s="4" t="n">
         <v>143.37</v>
       </c>
+      <c r="U5" s="4" t="n">
+        <v>119.03</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>168.4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -8849,7 +9445,13 @@
         <v>82.34</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>62.19</v>
+        <v>75.12</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>40.14</v>
       </c>
     </row>
     <row r="7">
@@ -8915,6 +9517,12 @@
       <c r="T7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="U7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -8979,6 +9587,12 @@
       <c r="T8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="U8" s="4" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>6.45</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -9043,6 +9657,12 @@
       <c r="T9" s="4" t="n">
         <v>80.27</v>
       </c>
+      <c r="U9" s="4" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>59.32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -9107,6 +9727,12 @@
       <c r="T10" s="4" t="n">
         <v>77.83</v>
       </c>
+      <c r="U10" s="4" t="n">
+        <v>82.94</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>70.04000000000001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -9171,6 +9797,12 @@
       <c r="T11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="U11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -9235,6 +9867,12 @@
       <c r="T12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="U12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -9299,6 +9937,12 @@
       <c r="T13" s="4" t="n">
         <v>134.68</v>
       </c>
+      <c r="U13" s="4" t="n">
+        <v>117.61</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>143.94</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -9363,6 +10007,12 @@
       <c r="T14" s="4" t="n">
         <v>194.68</v>
       </c>
+      <c r="U14" s="4" t="n">
+        <v>127.22</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>159.81</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -9425,7 +10075,13 @@
         <v>133.96</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>84.5</v>
+        <v>89.68000000000001</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>94.79000000000001</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -9486,10 +10142,16 @@
         <v>20.09</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>14.16</v>
+        <v>15.82</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>18.58</v>
+        <v>19.81</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>27.04</v>
       </c>
     </row>
     <row r="17">
@@ -9555,6 +10217,12 @@
       <c r="T17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="U17" s="4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>1.18</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -9617,7 +10285,13 @@
         <v>248.65</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>168.38</v>
+        <v>171.51</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>147.68</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>187.21</v>
       </c>
     </row>
     <row r="19">
@@ -9683,6 +10357,12 @@
       <c r="T19" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="U19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -9747,1292 +10427,1456 @@
       <c r="T20" s="4" t="n">
         <v>50.33</v>
       </c>
+      <c r="U20" s="4" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>78.39</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Avaada Electro Limited</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>220.36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="28">
-        <f>SUM(B5:B20)</f>
-        <v/>
-      </c>
-      <c r="C21" s="28">
-        <f>SUM(C5:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="28">
-        <f>SUM(D5:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="28">
-        <f>SUM(E5:E20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="28">
-        <f>SUM(F5:F20)</f>
-        <v/>
-      </c>
-      <c r="G21" s="28">
-        <f>SUM(G5:G20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="28">
-        <f>SUM(H5:H20)</f>
-        <v/>
-      </c>
-      <c r="I21" s="28">
-        <f>SUM(I5:I20)</f>
-        <v/>
-      </c>
-      <c r="J21" s="28">
-        <f>SUM(J5:J20)</f>
-        <v/>
-      </c>
-      <c r="K21" s="28">
-        <f>SUM(K5:K20)</f>
-        <v/>
-      </c>
-      <c r="L21" s="28">
-        <f>SUM(L5:L20)</f>
-        <v/>
-      </c>
-      <c r="M21" s="28">
-        <f>SUM(M5:M20)</f>
-        <v/>
-      </c>
-      <c r="N21" s="28">
-        <f>SUM(N5:N20)</f>
-        <v/>
-      </c>
-      <c r="O21" s="28">
-        <f>SUM(O5:O20)</f>
-        <v/>
-      </c>
-      <c r="P21" s="28">
-        <f>SUM(P5:P20)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="28">
-        <f>SUM(Q5:Q20)</f>
-        <v/>
-      </c>
-      <c r="R21" s="28">
-        <f>SUM(R5:R20)</f>
-        <v/>
-      </c>
-      <c r="S21" s="28">
-        <f>SUM(S5:S20)</f>
-        <v/>
-      </c>
-      <c r="T21" s="28">
-        <f>SUM(T5:T20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="17.25" customHeight="1">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="B22" s="28">
+        <f>SUM(B5:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="28">
+        <f>SUM(C5:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>SUM(D5:D21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="28">
+        <f>SUM(E5:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="28">
+        <f>SUM(F5:F21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="28">
+        <f>SUM(G5:G21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="28">
+        <f>SUM(H5:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="28">
+        <f>SUM(I5:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="28">
+        <f>SUM(J5:J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="28">
+        <f>SUM(K5:K21)</f>
+        <v/>
+      </c>
+      <c r="L22" s="28">
+        <f>SUM(L5:L21)</f>
+        <v/>
+      </c>
+      <c r="M22" s="28">
+        <f>SUM(M5:M21)</f>
+        <v/>
+      </c>
+      <c r="N22" s="28">
+        <f>SUM(N5:N21)</f>
+        <v/>
+      </c>
+      <c r="O22" s="28">
+        <f>SUM(O5:O21)</f>
+        <v/>
+      </c>
+      <c r="P22" s="28">
+        <f>SUM(P5:P21)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="28">
+        <f>SUM(Q5:Q21)</f>
+        <v/>
+      </c>
+      <c r="R22" s="28">
+        <f>SUM(R5:R21)</f>
+        <v/>
+      </c>
+      <c r="S22" s="28">
+        <f>SUM(S5:S21)</f>
+        <v/>
+      </c>
+      <c r="T22" s="28">
+        <f>SUM(T5:T21)</f>
+        <v/>
+      </c>
+      <c r="U22" s="28">
+        <f>SUM(U5:U21)</f>
+        <v/>
+      </c>
+      <c r="V22" s="28">
+        <f>SUM(V5:V21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24" ht="17.25" customHeight="1"/>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>Summary — Key Players (MW)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>2025 (MW)</t>
         </is>
       </c>
-      <c r="N25" s="31" t="inlineStr">
+      <c r="N26" s="31" t="inlineStr">
         <is>
           <t>2026 (MW)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="31" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D26" s="31" t="inlineStr">
+      <c r="D27" s="31" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E26" s="31" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F26" s="31" t="inlineStr">
+      <c r="F27" s="31" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G26" s="31" t="inlineStr">
+      <c r="G27" s="31" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H26" s="31" t="inlineStr">
+      <c r="H27" s="31" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I26" s="31" t="inlineStr">
+      <c r="I27" s="31" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J26" s="31" t="inlineStr">
+      <c r="J27" s="31" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K26" s="31" t="inlineStr">
+      <c r="K27" s="31" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L26" s="31" t="inlineStr">
+      <c r="L27" s="31" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M26" s="31" t="inlineStr">
+      <c r="M27" s="31" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N26" s="31" t="inlineStr">
+      <c r="N27" s="31" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="O26" s="31" t="inlineStr">
+      <c r="O27" s="31" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="P26" s="31" t="inlineStr">
+      <c r="P27" s="31" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="Q26" s="31" t="inlineStr">
+      <c r="Q27" s="31" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="R26" s="31" t="inlineStr">
+      <c r="R27" s="31" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="S26" s="31" t="inlineStr">
+      <c r="S27" s="31" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="T26" s="31" t="inlineStr">
+      <c r="T27" s="31" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="B27" s="4">
-        <f>B17+B18</f>
-        <v/>
-      </c>
-      <c r="C27" s="4">
-        <f>C17+C18</f>
-        <v/>
-      </c>
-      <c r="D27" s="4">
-        <f>D17+D18</f>
-        <v/>
-      </c>
-      <c r="E27" s="4">
-        <f>E17+E18</f>
-        <v/>
-      </c>
-      <c r="F27" s="4">
-        <f>F17+F18</f>
-        <v/>
-      </c>
-      <c r="G27" s="4">
-        <f>G17+G18</f>
-        <v/>
-      </c>
-      <c r="H27" s="4">
-        <f>H17+H18</f>
-        <v/>
-      </c>
-      <c r="I27" s="4">
-        <f>I17+I18</f>
-        <v/>
-      </c>
-      <c r="J27" s="4">
-        <f>J17+J18</f>
-        <v/>
-      </c>
-      <c r="K27" s="4">
-        <f>K17+K18</f>
-        <v/>
-      </c>
-      <c r="L27" s="4">
-        <f>L17+L18</f>
-        <v/>
-      </c>
-      <c r="M27" s="4">
-        <f>M17+M18</f>
-        <v/>
-      </c>
-      <c r="N27" s="4">
-        <f>N17+N18</f>
-        <v/>
-      </c>
-      <c r="O27" s="4">
-        <f>O17+O18</f>
-        <v/>
-      </c>
-      <c r="P27" s="4">
-        <f>P17+P18</f>
-        <v/>
-      </c>
-      <c r="Q27" s="4">
-        <f>Q17+Q18</f>
-        <v/>
-      </c>
-      <c r="R27" s="4">
-        <f>R17+R18</f>
-        <v/>
-      </c>
-      <c r="S27" s="4">
-        <f>S17+S18</f>
-        <v/>
-      </c>
-      <c r="T27" s="4">
-        <f>T17+T18</f>
-        <v/>
+      <c r="U27" s="31" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="V27" s="31" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Adani</t>
+          <t>Tata Power</t>
         </is>
       </c>
       <c r="B28" s="4">
-        <f>B11+B12</f>
+        <f>B17+B18</f>
         <v/>
       </c>
       <c r="C28" s="4">
-        <f>C11+C12</f>
+        <f>C17+C18</f>
         <v/>
       </c>
       <c r="D28" s="4">
-        <f>D11+D12</f>
+        <f>D17+D18</f>
         <v/>
       </c>
       <c r="E28" s="4">
-        <f>E11+E12</f>
+        <f>E17+E18</f>
         <v/>
       </c>
       <c r="F28" s="4">
-        <f>F11+F12</f>
+        <f>F17+F18</f>
         <v/>
       </c>
       <c r="G28" s="4">
-        <f>G11+G12</f>
+        <f>G17+G18</f>
         <v/>
       </c>
       <c r="H28" s="4">
-        <f>H11+H12</f>
+        <f>H17+H18</f>
         <v/>
       </c>
       <c r="I28" s="4">
-        <f>I11+I12</f>
+        <f>I17+I18</f>
         <v/>
       </c>
       <c r="J28" s="4">
-        <f>J11+J12</f>
+        <f>J17+J18</f>
         <v/>
       </c>
       <c r="K28" s="4">
-        <f>K11+K12</f>
+        <f>K17+K18</f>
         <v/>
       </c>
       <c r="L28" s="4">
-        <f>L11+L12</f>
+        <f>L17+L18</f>
         <v/>
       </c>
       <c r="M28" s="4">
-        <f>M11+M12</f>
+        <f>M17+M18</f>
         <v/>
       </c>
       <c r="N28" s="4">
-        <f>N11+N12</f>
+        <f>N17+N18</f>
         <v/>
       </c>
       <c r="O28" s="4">
-        <f>O11+O12</f>
+        <f>O17+O18</f>
         <v/>
       </c>
       <c r="P28" s="4">
-        <f>P11+P12</f>
+        <f>P17+P18</f>
         <v/>
       </c>
       <c r="Q28" s="4">
-        <f>Q11+Q12</f>
+        <f>Q17+Q18</f>
         <v/>
       </c>
       <c r="R28" s="4">
-        <f>R11+R12</f>
+        <f>R17+R18</f>
         <v/>
       </c>
       <c r="S28" s="4">
-        <f>S11+S12</f>
+        <f>S17+S18</f>
         <v/>
       </c>
       <c r="T28" s="4">
-        <f>T11+T12</f>
+        <f>T17+T18</f>
+        <v/>
+      </c>
+      <c r="U28" s="4">
+        <f>U17+U18</f>
+        <v/>
+      </c>
+      <c r="V28" s="4">
+        <f>V17+V18</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>FS India Solar</t>
+          <t>Adani</t>
         </is>
       </c>
       <c r="B29" s="4">
-        <f>B7</f>
+        <f>B11+B12</f>
         <v/>
       </c>
       <c r="C29" s="4">
-        <f>C7</f>
+        <f>C11+C12</f>
         <v/>
       </c>
       <c r="D29" s="4">
-        <f>D7</f>
+        <f>D11+D12</f>
         <v/>
       </c>
       <c r="E29" s="4">
-        <f>E7</f>
+        <f>E11+E12</f>
         <v/>
       </c>
       <c r="F29" s="4">
-        <f>F7</f>
+        <f>F11+F12</f>
         <v/>
       </c>
       <c r="G29" s="4">
-        <f>G7</f>
+        <f>G11+G12</f>
         <v/>
       </c>
       <c r="H29" s="4">
-        <f>H7</f>
+        <f>H11+H12</f>
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>I7</f>
+        <f>I11+I12</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>J7</f>
+        <f>J11+J12</f>
         <v/>
       </c>
       <c r="K29" s="4">
-        <f>K7</f>
+        <f>K11+K12</f>
         <v/>
       </c>
       <c r="L29" s="4">
-        <f>L7</f>
+        <f>L11+L12</f>
         <v/>
       </c>
       <c r="M29" s="4">
-        <f>M7</f>
+        <f>M11+M12</f>
         <v/>
       </c>
       <c r="N29" s="4">
-        <f>N7</f>
+        <f>N11+N12</f>
         <v/>
       </c>
       <c r="O29" s="4">
-        <f>O7</f>
+        <f>O11+O12</f>
         <v/>
       </c>
       <c r="P29" s="4">
-        <f>P7</f>
+        <f>P11+P12</f>
         <v/>
       </c>
       <c r="Q29" s="4">
-        <f>Q7</f>
+        <f>Q11+Q12</f>
         <v/>
       </c>
       <c r="R29" s="4">
-        <f>R7</f>
+        <f>R11+R12</f>
         <v/>
       </c>
       <c r="S29" s="4">
-        <f>S7</f>
+        <f>S11+S12</f>
         <v/>
       </c>
       <c r="T29" s="4">
-        <f>T7</f>
+        <f>T11+T12</f>
+        <v/>
+      </c>
+      <c r="U29" s="4">
+        <f>U11+U12</f>
+        <v/>
+      </c>
+      <c r="V29" s="4">
+        <f>V11+V12</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Waaree Energies</t>
+          <t>FS India Solar</t>
         </is>
       </c>
       <c r="B30" s="4">
-        <f>B19</f>
+        <f>B7</f>
         <v/>
       </c>
       <c r="C30" s="4">
-        <f>C19</f>
+        <f>C7</f>
         <v/>
       </c>
       <c r="D30" s="4">
-        <f>D19</f>
+        <f>D7</f>
         <v/>
       </c>
       <c r="E30" s="4">
-        <f>E19</f>
+        <f>E7</f>
         <v/>
       </c>
       <c r="F30" s="4">
-        <f>F19</f>
+        <f>F7</f>
         <v/>
       </c>
       <c r="G30" s="4">
-        <f>G19</f>
+        <f>G7</f>
         <v/>
       </c>
       <c r="H30" s="4">
-        <f>H19</f>
+        <f>H7</f>
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>I19</f>
+        <f>I7</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>J19</f>
+        <f>J7</f>
         <v/>
       </c>
       <c r="K30" s="4">
-        <f>K19</f>
+        <f>K7</f>
         <v/>
       </c>
       <c r="L30" s="4">
-        <f>L19</f>
+        <f>L7</f>
         <v/>
       </c>
       <c r="M30" s="4">
-        <f>M19</f>
+        <f>M7</f>
         <v/>
       </c>
       <c r="N30" s="4">
-        <f>N19</f>
+        <f>N7</f>
         <v/>
       </c>
       <c r="O30" s="4">
-        <f>O19</f>
+        <f>O7</f>
         <v/>
       </c>
       <c r="P30" s="4">
-        <f>P19</f>
+        <f>P7</f>
         <v/>
       </c>
       <c r="Q30" s="4">
-        <f>Q19</f>
+        <f>Q7</f>
         <v/>
       </c>
       <c r="R30" s="4">
-        <f>R19</f>
+        <f>R7</f>
         <v/>
       </c>
       <c r="S30" s="4">
-        <f>S19</f>
+        <f>S7</f>
         <v/>
       </c>
       <c r="T30" s="4">
-        <f>T19</f>
+        <f>T7</f>
+        <v/>
+      </c>
+      <c r="U30" s="4">
+        <f>U7</f>
+        <v/>
+      </c>
+      <c r="V30" s="4">
+        <f>V7</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Premier Energies</t>
+          <t>Waaree Energies</t>
         </is>
       </c>
       <c r="B31" s="4">
-        <f>B13+B14</f>
+        <f>B19</f>
         <v/>
       </c>
       <c r="C31" s="4">
-        <f>C13+C14</f>
+        <f>C19</f>
         <v/>
       </c>
       <c r="D31" s="4">
-        <f>D13+D14</f>
+        <f>D19</f>
         <v/>
       </c>
       <c r="E31" s="4">
-        <f>E13+E14</f>
+        <f>E19</f>
         <v/>
       </c>
       <c r="F31" s="4">
-        <f>F13+F14</f>
+        <f>F19</f>
         <v/>
       </c>
       <c r="G31" s="4">
-        <f>G13+G14</f>
+        <f>G19</f>
         <v/>
       </c>
       <c r="H31" s="4">
-        <f>H13+H14</f>
+        <f>H19</f>
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>I13+I14</f>
+        <f>I19</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>J13+J14</f>
+        <f>J19</f>
         <v/>
       </c>
       <c r="K31" s="4">
-        <f>K13+K14</f>
+        <f>K19</f>
         <v/>
       </c>
       <c r="L31" s="4">
-        <f>L13+L14</f>
+        <f>L19</f>
         <v/>
       </c>
       <c r="M31" s="4">
-        <f>M13+M14</f>
+        <f>M19</f>
         <v/>
       </c>
       <c r="N31" s="4">
-        <f>N13+N14</f>
+        <f>N19</f>
         <v/>
       </c>
       <c r="O31" s="4">
-        <f>O13+O14</f>
+        <f>O19</f>
         <v/>
       </c>
       <c r="P31" s="4">
-        <f>P13+P14</f>
+        <f>P19</f>
         <v/>
       </c>
       <c r="Q31" s="4">
-        <f>Q13+Q14</f>
+        <f>Q19</f>
         <v/>
       </c>
       <c r="R31" s="4">
-        <f>R13+R14</f>
+        <f>R19</f>
         <v/>
       </c>
       <c r="S31" s="4">
-        <f>S13+S14</f>
+        <f>S19</f>
         <v/>
       </c>
       <c r="T31" s="4">
-        <f>T13+T14</f>
+        <f>T19</f>
+        <v/>
+      </c>
+      <c r="U31" s="4">
+        <f>U19</f>
+        <v/>
+      </c>
+      <c r="V31" s="4">
+        <f>V19</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Jupiter International</t>
+          <t>Premier Energies</t>
         </is>
       </c>
       <c r="B32" s="4">
-        <f>B9+B10</f>
+        <f>B13+B14</f>
         <v/>
       </c>
       <c r="C32" s="4">
-        <f>C9+C10</f>
+        <f>C13+C14</f>
         <v/>
       </c>
       <c r="D32" s="4">
-        <f>D9+D10</f>
+        <f>D13+D14</f>
         <v/>
       </c>
       <c r="E32" s="4">
-        <f>E9+E10</f>
+        <f>E13+E14</f>
         <v/>
       </c>
       <c r="F32" s="4">
-        <f>F9+F10</f>
+        <f>F13+F14</f>
         <v/>
       </c>
       <c r="G32" s="4">
-        <f>G9+G10</f>
+        <f>G13+G14</f>
         <v/>
       </c>
       <c r="H32" s="4">
-        <f>H9+H10</f>
+        <f>H13+H14</f>
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>I9+I10</f>
+        <f>I13+I14</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>J9+J10</f>
+        <f>J13+J14</f>
         <v/>
       </c>
       <c r="K32" s="4">
-        <f>K9+K10</f>
+        <f>K13+K14</f>
         <v/>
       </c>
       <c r="L32" s="4">
-        <f>L9+L10</f>
+        <f>L13+L14</f>
         <v/>
       </c>
       <c r="M32" s="4">
-        <f>M9+M10</f>
+        <f>M13+M14</f>
         <v/>
       </c>
       <c r="N32" s="4">
-        <f>N9+N10</f>
+        <f>N13+N14</f>
         <v/>
       </c>
       <c r="O32" s="4">
-        <f>O9+O10</f>
+        <f>O13+O14</f>
         <v/>
       </c>
       <c r="P32" s="4">
-        <f>P9+P10</f>
+        <f>P13+P14</f>
         <v/>
       </c>
       <c r="Q32" s="4">
-        <f>Q9+Q10</f>
+        <f>Q13+Q14</f>
         <v/>
       </c>
       <c r="R32" s="4">
-        <f>R9+R10</f>
+        <f>R13+R14</f>
         <v/>
       </c>
       <c r="S32" s="4">
-        <f>S9+S10</f>
+        <f>S13+S14</f>
         <v/>
       </c>
       <c r="T32" s="4">
-        <f>T9+T10</f>
+        <f>T13+T14</f>
+        <v/>
+      </c>
+      <c r="U32" s="4">
+        <f>U13+U14</f>
+        <v/>
+      </c>
+      <c r="V32" s="4">
+        <f>V13+V14</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Websol Energy System</t>
+          <t>Jupiter International</t>
         </is>
       </c>
       <c r="B33" s="4">
-        <f>B20</f>
+        <f>B9+B10</f>
         <v/>
       </c>
       <c r="C33" s="4">
-        <f>C20</f>
+        <f>C9+C10</f>
         <v/>
       </c>
       <c r="D33" s="4">
-        <f>D20</f>
+        <f>D9+D10</f>
         <v/>
       </c>
       <c r="E33" s="4">
-        <f>E20</f>
+        <f>E9+E10</f>
         <v/>
       </c>
       <c r="F33" s="4">
-        <f>F20</f>
+        <f>F9+F10</f>
         <v/>
       </c>
       <c r="G33" s="4">
-        <f>G20</f>
+        <f>G9+G10</f>
         <v/>
       </c>
       <c r="H33" s="4">
-        <f>H20</f>
+        <f>H9+H10</f>
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>I20</f>
+        <f>I9+I10</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>J20</f>
+        <f>J9+J10</f>
         <v/>
       </c>
       <c r="K33" s="4">
-        <f>K20</f>
+        <f>K9+K10</f>
         <v/>
       </c>
       <c r="L33" s="4">
-        <f>L20</f>
+        <f>L9+L10</f>
         <v/>
       </c>
       <c r="M33" s="4">
-        <f>M20</f>
+        <f>M9+M10</f>
         <v/>
       </c>
       <c r="N33" s="4">
-        <f>N20</f>
+        <f>N9+N10</f>
         <v/>
       </c>
       <c r="O33" s="4">
-        <f>O20</f>
+        <f>O9+O10</f>
         <v/>
       </c>
       <c r="P33" s="4">
-        <f>P20</f>
+        <f>P9+P10</f>
         <v/>
       </c>
       <c r="Q33" s="4">
-        <f>Q20</f>
+        <f>Q9+Q10</f>
         <v/>
       </c>
       <c r="R33" s="4">
-        <f>R20</f>
+        <f>R9+R10</f>
         <v/>
       </c>
       <c r="S33" s="4">
-        <f>S20</f>
+        <f>S9+S10</f>
         <v/>
       </c>
       <c r="T33" s="4">
-        <f>T20</f>
+        <f>T9+T10</f>
+        <v/>
+      </c>
+      <c r="U33" s="4">
+        <f>U9+U10</f>
+        <v/>
+      </c>
+      <c r="V33" s="4">
+        <f>V9+V10</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Evervolt Solar Technology</t>
+          <t>Websol Energy System</t>
         </is>
       </c>
       <c r="B34" s="4">
-        <f>B6</f>
+        <f>B20</f>
         <v/>
       </c>
       <c r="C34" s="4">
-        <f>C6</f>
+        <f>C20</f>
         <v/>
       </c>
       <c r="D34" s="4">
-        <f>D6</f>
+        <f>D20</f>
         <v/>
       </c>
       <c r="E34" s="4">
-        <f>E6</f>
+        <f>E20</f>
         <v/>
       </c>
       <c r="F34" s="4">
-        <f>F6</f>
+        <f>F20</f>
         <v/>
       </c>
       <c r="G34" s="4">
-        <f>G6</f>
+        <f>G20</f>
         <v/>
       </c>
       <c r="H34" s="4">
-        <f>H6</f>
+        <f>H20</f>
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>I6</f>
+        <f>I20</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>J6</f>
+        <f>J20</f>
         <v/>
       </c>
       <c r="K34" s="4">
-        <f>K6</f>
+        <f>K20</f>
         <v/>
       </c>
       <c r="L34" s="4">
-        <f>L6</f>
+        <f>L20</f>
         <v/>
       </c>
       <c r="M34" s="4">
-        <f>M6</f>
+        <f>M20</f>
         <v/>
       </c>
       <c r="N34" s="4">
-        <f>N6</f>
+        <f>N20</f>
         <v/>
       </c>
       <c r="O34" s="4">
-        <f>O6</f>
+        <f>O20</f>
         <v/>
       </c>
       <c r="P34" s="4">
-        <f>P6</f>
+        <f>P20</f>
         <v/>
       </c>
       <c r="Q34" s="4">
-        <f>Q6</f>
+        <f>Q20</f>
         <v/>
       </c>
       <c r="R34" s="4">
-        <f>R6</f>
+        <f>R20</f>
         <v/>
       </c>
       <c r="S34" s="4">
-        <f>S6</f>
+        <f>S20</f>
         <v/>
       </c>
       <c r="T34" s="4">
-        <f>T6</f>
+        <f>T20</f>
+        <v/>
+      </c>
+      <c r="U34" s="4">
+        <f>U20</f>
+        <v/>
+      </c>
+      <c r="V34" s="4">
+        <f>V20</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Renew Photovoltaics</t>
+          <t>Evervolt Solar Technology</t>
         </is>
       </c>
       <c r="B35" s="4">
-        <f>B15</f>
+        <f>B6</f>
         <v/>
       </c>
       <c r="C35" s="4">
-        <f>C15</f>
+        <f>C6</f>
         <v/>
       </c>
       <c r="D35" s="4">
-        <f>D15</f>
+        <f>D6</f>
         <v/>
       </c>
       <c r="E35" s="4">
-        <f>E15</f>
+        <f>E6</f>
         <v/>
       </c>
       <c r="F35" s="4">
-        <f>F15</f>
+        <f>F6</f>
         <v/>
       </c>
       <c r="G35" s="4">
-        <f>G15</f>
+        <f>G6</f>
         <v/>
       </c>
       <c r="H35" s="4">
-        <f>H15</f>
+        <f>H6</f>
         <v/>
       </c>
       <c r="I35" s="4">
-        <f>I15</f>
+        <f>I6</f>
         <v/>
       </c>
       <c r="J35" s="4">
-        <f>J15</f>
+        <f>J6</f>
         <v/>
       </c>
       <c r="K35" s="4">
-        <f>K15</f>
+        <f>K6</f>
         <v/>
       </c>
       <c r="L35" s="4">
-        <f>L15</f>
+        <f>L6</f>
         <v/>
       </c>
       <c r="M35" s="4">
-        <f>M15</f>
+        <f>M6</f>
         <v/>
       </c>
       <c r="N35" s="4">
-        <f>N15</f>
+        <f>N6</f>
         <v/>
       </c>
       <c r="O35" s="4">
-        <f>O15</f>
+        <f>O6</f>
         <v/>
       </c>
       <c r="P35" s="4">
-        <f>P15</f>
+        <f>P6</f>
         <v/>
       </c>
       <c r="Q35" s="4">
-        <f>Q15</f>
+        <f>Q6</f>
         <v/>
       </c>
       <c r="R35" s="4">
-        <f>R15</f>
+        <f>R6</f>
         <v/>
       </c>
       <c r="S35" s="4">
-        <f>S15</f>
+        <f>S6</f>
         <v/>
       </c>
       <c r="T35" s="4">
-        <f>T15</f>
+        <f>T6</f>
+        <v/>
+      </c>
+      <c r="U35" s="4">
+        <f>U6</f>
+        <v/>
+      </c>
+      <c r="V35" s="4">
+        <f>V6</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Emmvee</t>
+          <t>Renew Photovoltaics</t>
         </is>
       </c>
       <c r="B36" s="4">
-        <f>B5</f>
+        <f>B15</f>
         <v/>
       </c>
       <c r="C36" s="4">
-        <f>C5</f>
+        <f>C15</f>
         <v/>
       </c>
       <c r="D36" s="4">
-        <f>D5</f>
+        <f>D15</f>
         <v/>
       </c>
       <c r="E36" s="4">
-        <f>E5</f>
+        <f>E15</f>
         <v/>
       </c>
       <c r="F36" s="4">
-        <f>F5</f>
+        <f>F15</f>
         <v/>
       </c>
       <c r="G36" s="4">
-        <f>G5</f>
+        <f>G15</f>
         <v/>
       </c>
       <c r="H36" s="4">
-        <f>H5</f>
+        <f>H15</f>
         <v/>
       </c>
       <c r="I36" s="4">
-        <f>I5</f>
+        <f>I15</f>
         <v/>
       </c>
       <c r="J36" s="4">
-        <f>J5</f>
+        <f>J15</f>
         <v/>
       </c>
       <c r="K36" s="4">
-        <f>K5</f>
+        <f>K15</f>
         <v/>
       </c>
       <c r="L36" s="4">
-        <f>L5</f>
+        <f>L15</f>
         <v/>
       </c>
       <c r="M36" s="4">
-        <f>M5</f>
+        <f>M15</f>
         <v/>
       </c>
       <c r="N36" s="4">
-        <f>N5</f>
+        <f>N15</f>
         <v/>
       </c>
       <c r="O36" s="4">
-        <f>O5</f>
+        <f>O15</f>
         <v/>
       </c>
       <c r="P36" s="4">
-        <f>P5</f>
+        <f>P15</f>
         <v/>
       </c>
       <c r="Q36" s="4">
-        <f>Q5</f>
+        <f>Q15</f>
         <v/>
       </c>
       <c r="R36" s="4">
-        <f>R5</f>
+        <f>R15</f>
         <v/>
       </c>
       <c r="S36" s="4">
-        <f>S5</f>
+        <f>S15</f>
         <v/>
       </c>
       <c r="T36" s="4">
-        <f>T5</f>
+        <f>T15</f>
+        <v/>
+      </c>
+      <c r="U36" s="4">
+        <f>U15</f>
+        <v/>
+      </c>
+      <c r="V36" s="4">
+        <f>V15</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>Emmvee</t>
+        </is>
+      </c>
+      <c r="B37" s="4">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C37" s="4">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D37" s="4">
+        <f>D5</f>
+        <v/>
+      </c>
+      <c r="E37" s="4">
+        <f>E5</f>
+        <v/>
+      </c>
+      <c r="F37" s="4">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="G37" s="4">
+        <f>G5</f>
+        <v/>
+      </c>
+      <c r="H37" s="4">
+        <f>H5</f>
+        <v/>
+      </c>
+      <c r="I37" s="4">
+        <f>I5</f>
+        <v/>
+      </c>
+      <c r="J37" s="4">
+        <f>J5</f>
+        <v/>
+      </c>
+      <c r="K37" s="4">
+        <f>K5</f>
+        <v/>
+      </c>
+      <c r="L37" s="4">
+        <f>L5</f>
+        <v/>
+      </c>
+      <c r="M37" s="4">
+        <f>M5</f>
+        <v/>
+      </c>
+      <c r="N37" s="4">
+        <f>N5</f>
+        <v/>
+      </c>
+      <c r="O37" s="4">
+        <f>O5</f>
+        <v/>
+      </c>
+      <c r="P37" s="4">
+        <f>P5</f>
+        <v/>
+      </c>
+      <c r="Q37" s="4">
+        <f>Q5</f>
+        <v/>
+      </c>
+      <c r="R37" s="4">
+        <f>R5</f>
+        <v/>
+      </c>
+      <c r="S37" s="4">
+        <f>S5</f>
+        <v/>
+      </c>
+      <c r="T37" s="4">
+        <f>T5</f>
+        <v/>
+      </c>
+      <c r="U37" s="4">
+        <f>U5</f>
+        <v/>
+      </c>
+      <c r="V37" s="4">
+        <f>V5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
           <t>Others</t>
         </is>
       </c>
-      <c r="B37" s="4">
-        <f>B21-SUM(B27:B36)</f>
-        <v/>
-      </c>
-      <c r="C37" s="4">
-        <f>C21-SUM(C27:C36)</f>
-        <v/>
-      </c>
-      <c r="D37" s="4">
-        <f>D21-SUM(D27:D36)</f>
-        <v/>
-      </c>
-      <c r="E37" s="4">
-        <f>E21-SUM(E27:E36)</f>
-        <v/>
-      </c>
-      <c r="F37" s="4">
-        <f>F21-SUM(F27:F36)</f>
-        <v/>
-      </c>
-      <c r="G37" s="4">
-        <f>G21-SUM(G27:G36)</f>
-        <v/>
-      </c>
-      <c r="H37" s="4">
-        <f>H21-SUM(H27:H36)</f>
-        <v/>
-      </c>
-      <c r="I37" s="4">
-        <f>I21-SUM(I27:I36)</f>
-        <v/>
-      </c>
-      <c r="J37" s="4">
-        <f>J21-SUM(J27:J36)</f>
-        <v/>
-      </c>
-      <c r="K37" s="4">
-        <f>K21-SUM(K27:K36)</f>
-        <v/>
-      </c>
-      <c r="L37" s="4">
-        <f>L21-SUM(L27:L36)</f>
-        <v/>
-      </c>
-      <c r="M37" s="4">
-        <f>M21-SUM(M27:M36)</f>
-        <v/>
-      </c>
-      <c r="N37" s="4">
-        <f>N21-SUM(N27:N36)</f>
-        <v/>
-      </c>
-      <c r="O37" s="4">
-        <f>O21-SUM(O27:O36)</f>
-        <v/>
-      </c>
-      <c r="P37" s="4">
-        <f>P21-SUM(P27:P36)</f>
-        <v/>
-      </c>
-      <c r="Q37" s="4">
-        <f>Q21-SUM(Q27:Q36)</f>
-        <v/>
-      </c>
-      <c r="R37" s="4">
-        <f>R21-SUM(R27:R36)</f>
-        <v/>
-      </c>
-      <c r="S37" s="4">
-        <f>S21-SUM(S27:S36)</f>
-        <v/>
-      </c>
-      <c r="T37" s="4">
-        <f>T21-SUM(T27:T36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="B38" s="4">
+        <f>B22-SUM(B28:B37)</f>
+        <v/>
+      </c>
+      <c r="C38" s="4">
+        <f>C22-SUM(C28:C37)</f>
+        <v/>
+      </c>
+      <c r="D38" s="4">
+        <f>D22-SUM(D28:D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="4">
+        <f>E22-SUM(E28:E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="4">
+        <f>F22-SUM(F28:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="4">
+        <f>G22-SUM(G28:G37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="4">
+        <f>H22-SUM(H28:H37)</f>
+        <v/>
+      </c>
+      <c r="I38" s="4">
+        <f>I22-SUM(I28:I37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="4">
+        <f>J22-SUM(J28:J37)</f>
+        <v/>
+      </c>
+      <c r="K38" s="4">
+        <f>K22-SUM(K28:K37)</f>
+        <v/>
+      </c>
+      <c r="L38" s="4">
+        <f>L22-SUM(L28:L37)</f>
+        <v/>
+      </c>
+      <c r="M38" s="4">
+        <f>M22-SUM(M28:M37)</f>
+        <v/>
+      </c>
+      <c r="N38" s="4">
+        <f>N22-SUM(N28:N37)</f>
+        <v/>
+      </c>
+      <c r="O38" s="4">
+        <f>O22-SUM(O28:O37)</f>
+        <v/>
+      </c>
+      <c r="P38" s="4">
+        <f>P22-SUM(P28:P37)</f>
+        <v/>
+      </c>
+      <c r="Q38" s="4">
+        <f>Q22-SUM(Q28:Q37)</f>
+        <v/>
+      </c>
+      <c r="R38" s="4">
+        <f>R22-SUM(R28:R37)</f>
+        <v/>
+      </c>
+      <c r="S38" s="4">
+        <f>S22-SUM(S28:S37)</f>
+        <v/>
+      </c>
+      <c r="T38" s="4">
+        <f>T22-SUM(T28:T37)</f>
+        <v/>
+      </c>
+      <c r="U38" s="4">
+        <f>U22-SUM(U28:U37)</f>
+        <v/>
+      </c>
+      <c r="V38" s="4">
+        <f>V22-SUM(V28:V37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="28">
-        <f>SUM(B27:B37)</f>
-        <v/>
-      </c>
-      <c r="C38" s="28">
-        <f>SUM(C27:C37)</f>
-        <v/>
-      </c>
-      <c r="D38" s="28">
-        <f>SUM(D27:D37)</f>
-        <v/>
-      </c>
-      <c r="E38" s="28">
-        <f>SUM(E27:E37)</f>
-        <v/>
-      </c>
-      <c r="F38" s="28">
-        <f>SUM(F27:F37)</f>
-        <v/>
-      </c>
-      <c r="G38" s="28">
-        <f>SUM(G27:G37)</f>
-        <v/>
-      </c>
-      <c r="H38" s="28">
-        <f>SUM(H27:H37)</f>
-        <v/>
-      </c>
-      <c r="I38" s="28">
-        <f>SUM(I27:I37)</f>
-        <v/>
-      </c>
-      <c r="J38" s="28">
-        <f>SUM(J27:J37)</f>
-        <v/>
-      </c>
-      <c r="K38" s="28">
-        <f>SUM(K27:K37)</f>
-        <v/>
-      </c>
-      <c r="L38" s="28">
-        <f>SUM(L27:L37)</f>
-        <v/>
-      </c>
-      <c r="M38" s="28">
-        <f>SUM(M27:M37)</f>
-        <v/>
-      </c>
-      <c r="N38" s="28">
-        <f>SUM(N27:N37)</f>
-        <v/>
-      </c>
-      <c r="O38" s="28">
-        <f>SUM(O27:O37)</f>
-        <v/>
-      </c>
-      <c r="P38" s="28">
-        <f>SUM(P27:P37)</f>
-        <v/>
-      </c>
-      <c r="Q38" s="28">
-        <f>SUM(Q27:Q37)</f>
-        <v/>
-      </c>
-      <c r="R38" s="28">
-        <f>SUM(R27:R37)</f>
-        <v/>
-      </c>
-      <c r="S38" s="28">
-        <f>SUM(S27:S37)</f>
-        <v/>
-      </c>
-      <c r="T38" s="28">
-        <f>SUM(T27:T37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="17.25" customHeight="1">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="B39" s="28">
+        <f>SUM(B28:B38)</f>
+        <v/>
+      </c>
+      <c r="C39" s="28">
+        <f>SUM(C28:C38)</f>
+        <v/>
+      </c>
+      <c r="D39" s="28">
+        <f>SUM(D28:D38)</f>
+        <v/>
+      </c>
+      <c r="E39" s="28">
+        <f>SUM(E28:E38)</f>
+        <v/>
+      </c>
+      <c r="F39" s="28">
+        <f>SUM(F28:F38)</f>
+        <v/>
+      </c>
+      <c r="G39" s="28">
+        <f>SUM(G28:G38)</f>
+        <v/>
+      </c>
+      <c r="H39" s="28">
+        <f>SUM(H28:H38)</f>
+        <v/>
+      </c>
+      <c r="I39" s="28">
+        <f>SUM(I28:I38)</f>
+        <v/>
+      </c>
+      <c r="J39" s="28">
+        <f>SUM(J28:J38)</f>
+        <v/>
+      </c>
+      <c r="K39" s="28">
+        <f>SUM(K28:K38)</f>
+        <v/>
+      </c>
+      <c r="L39" s="28">
+        <f>SUM(L28:L38)</f>
+        <v/>
+      </c>
+      <c r="M39" s="28">
+        <f>SUM(M28:M38)</f>
+        <v/>
+      </c>
+      <c r="N39" s="28">
+        <f>SUM(N28:N38)</f>
+        <v/>
+      </c>
+      <c r="O39" s="28">
+        <f>SUM(O28:O38)</f>
+        <v/>
+      </c>
+      <c r="P39" s="28">
+        <f>SUM(P28:P38)</f>
+        <v/>
+      </c>
+      <c r="Q39" s="28">
+        <f>SUM(Q28:Q38)</f>
+        <v/>
+      </c>
+      <c r="R39" s="28">
+        <f>SUM(R28:R38)</f>
+        <v/>
+      </c>
+      <c r="S39" s="28">
+        <f>SUM(S28:S38)</f>
+        <v/>
+      </c>
+      <c r="T39" s="28">
+        <f>SUM(T28:T38)</f>
+        <v/>
+      </c>
+      <c r="U39" s="28">
+        <f>SUM(U28:U38)</f>
+        <v/>
+      </c>
+      <c r="V39" s="28">
+        <f>SUM(V28:V38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="17.25" customHeight="1"/>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>DCR Cell Sales (MW) — Fiscal Year Summary</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="31" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="31" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B42" s="31" t="inlineStr">
+      <c r="B43" s="31" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="C42" s="31" t="inlineStr">
+      <c r="C43" s="31" t="inlineStr">
         <is>
           <t>FY26</t>
         </is>
       </c>
-      <c r="D42" s="31" t="inlineStr">
+      <c r="D43" s="31" t="inlineStr">
         <is>
           <t>Growth, %</t>
         </is>
       </c>
-      <c r="E42" s="31" t="inlineStr">
+      <c r="E43" s="31" t="inlineStr">
         <is>
           <t>YTD FY26</t>
         </is>
       </c>
-      <c r="F42" s="31" t="inlineStr">
+      <c r="F43" s="31" t="inlineStr">
         <is>
           <t>YTD FY27</t>
         </is>
       </c>
-      <c r="G42" s="31" t="inlineStr">
+      <c r="G43" s="31" t="inlineStr">
         <is>
           <t>Growth, %</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Premier Energies</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>1438</v>
-      </c>
-      <c r="C43" s="4">
-        <f>SUM(E31:P31)</f>
-        <v/>
-      </c>
-      <c r="D43" s="32">
-        <f>IF(B43=0,"NM",C43/B43-1)</f>
-        <v/>
-      </c>
-      <c r="E43" s="4">
-        <f>SUM(OFFSET(E31,0,0,1,COUNTA(Q$4:AB$4)))</f>
-        <v/>
-      </c>
-      <c r="F43" s="4">
-        <f>SUM(OFFSET(Q31,0,0,1,COUNTA(Q$4:AB$4)))</f>
-        <v/>
-      </c>
-      <c r="G43" s="32">
-        <f>IF(E43=0,"NM",F43/E43-1)</f>
-        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Adani</t>
+          <t>Premier Energies</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>361</v>
+        <v>1438</v>
       </c>
       <c r="C44" s="4">
-        <f>SUM(E28:P28)</f>
+        <f>SUM(E32:P32)</f>
         <v/>
       </c>
       <c r="D44" s="32">
@@ -11040,11 +11884,11 @@
         <v/>
       </c>
       <c r="E44" s="4">
-        <f>SUM(OFFSET(E28,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(E32,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="F44" s="4">
-        <f>SUM(OFFSET(Q28,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(Q32,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="G44" s="32">
@@ -11055,14 +11899,14 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Renew Photovoltaics</t>
+          <t>Adani</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>50</v>
+        <v>361</v>
       </c>
       <c r="C45" s="4">
-        <f>SUM(E35:P35)</f>
+        <f>SUM(E29:P29)</f>
         <v/>
       </c>
       <c r="D45" s="32">
@@ -11070,11 +11914,11 @@
         <v/>
       </c>
       <c r="E45" s="4">
-        <f>SUM(OFFSET(E35,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(E29,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="F45" s="4">
-        <f>SUM(OFFSET(Q35,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(Q29,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="G45" s="32">
@@ -11085,14 +11929,14 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Jupiter International</t>
+          <t>Renew Photovoltaics</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>491</v>
+        <v>50</v>
       </c>
       <c r="C46" s="4">
-        <f>SUM(E32:P32)</f>
+        <f>SUM(E36:P36)</f>
         <v/>
       </c>
       <c r="D46" s="32">
@@ -11100,11 +11944,11 @@
         <v/>
       </c>
       <c r="E46" s="4">
-        <f>SUM(OFFSET(E32,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(E36,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="F46" s="4">
-        <f>SUM(OFFSET(Q32,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(Q36,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="G46" s="32">
@@ -11115,14 +11959,14 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Tata Power</t>
+          <t>Jupiter International</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>272</v>
+        <v>491</v>
       </c>
       <c r="C47" s="4">
-        <f>SUM(E27:P27)</f>
+        <f>SUM(E33:P33)</f>
         <v/>
       </c>
       <c r="D47" s="32">
@@ -11130,11 +11974,11 @@
         <v/>
       </c>
       <c r="E47" s="4">
-        <f>SUM(OFFSET(E27,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(E33,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="F47" s="4">
-        <f>SUM(OFFSET(Q27,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(Q33,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="G47" s="32">
@@ -11145,14 +11989,14 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Websol Energy System</t>
+          <t>Tata Power</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>438</v>
+        <v>272</v>
       </c>
       <c r="C48" s="4">
-        <f>SUM(E33:P33)</f>
+        <f>SUM(E28:P28)</f>
         <v/>
       </c>
       <c r="D48" s="32">
@@ -11160,11 +12004,11 @@
         <v/>
       </c>
       <c r="E48" s="4">
-        <f>SUM(OFFSET(E33,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(E28,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="F48" s="4">
-        <f>SUM(OFFSET(Q33,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(Q28,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="G48" s="32">
@@ -11175,14 +12019,14 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Waaree Energies</t>
+          <t>Websol Energy System</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="C49" s="4">
-        <f>SUM(E30:P30)</f>
+        <f>SUM(E34:P34)</f>
         <v/>
       </c>
       <c r="D49" s="32">
@@ -11190,11 +12034,11 @@
         <v/>
       </c>
       <c r="E49" s="4">
-        <f>SUM(OFFSET(E30,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(E34,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="F49" s="4">
-        <f>SUM(OFFSET(Q30,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(Q34,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="G49" s="32">
@@ -11205,14 +12049,14 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Evervolt Solar Technology</t>
+          <t>Waaree Energies</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="4">
-        <f>SUM(E34:P34)</f>
+        <f>SUM(E31:P31)</f>
         <v/>
       </c>
       <c r="D50" s="32">
@@ -11220,11 +12064,11 @@
         <v/>
       </c>
       <c r="E50" s="4">
-        <f>SUM(OFFSET(E34,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(E31,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="F50" s="4">
-        <f>SUM(OFFSET(Q34,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(Q31,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="G50" s="32">
@@ -11235,14 +12079,14 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Emmvee</t>
+          <t>Evervolt Solar Technology</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="C51" s="4">
-        <f>SUM(E36:P36)</f>
+        <f>SUM(E35:P35)</f>
         <v/>
       </c>
       <c r="D51" s="32">
@@ -11250,11 +12094,11 @@
         <v/>
       </c>
       <c r="E51" s="4">
-        <f>SUM(OFFSET(E36,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(E35,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="F51" s="4">
-        <f>SUM(OFFSET(Q36,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <f>SUM(OFFSET(Q35,0,0,1,COUNTA(Q$4:AB$4)))</f>
         <v/>
       </c>
       <c r="G51" s="32">
@@ -11265,11 +12109,11 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Emmvee</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="C52" s="4">
         <f>SUM(E37:P37)</f>
@@ -11293,118 +12137,150 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="27" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="4">
+        <f>SUM(E38:P38)</f>
+        <v/>
+      </c>
+      <c r="D53" s="32">
+        <f>IF(B53=0,"NM",C53/B53-1)</f>
+        <v/>
+      </c>
+      <c r="E53" s="4">
+        <f>SUM(OFFSET(E38,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <v/>
+      </c>
+      <c r="F53" s="4">
+        <f>SUM(OFFSET(Q38,0,0,1,COUNTA(Q$4:AB$4)))</f>
+        <v/>
+      </c>
+      <c r="G53" s="32">
+        <f>IF(E53=0,"NM",F53/E53-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B53" s="28">
-        <f>SUM(B43:B52)</f>
-        <v/>
-      </c>
-      <c r="C53" s="28">
-        <f>SUM(C43:C52)</f>
-        <v/>
-      </c>
-      <c r="D53" s="33">
-        <f>IF(B53=0,"NM",C53/B53-1)</f>
-        <v/>
-      </c>
-      <c r="E53" s="28">
-        <f>SUM(E43:E52)</f>
-        <v/>
-      </c>
-      <c r="F53" s="28">
-        <f>SUM(F43:F52)</f>
-        <v/>
-      </c>
-      <c r="G53" s="33">
-        <f>IF(E53=0,"NM",F53/E53-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="34" t="n"/>
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B54" s="28">
+        <f>SUM(B44:B53)</f>
+        <v/>
+      </c>
+      <c r="C54" s="28">
+        <f>SUM(C44:C53)</f>
+        <v/>
+      </c>
+      <c r="D54" s="33">
+        <f>IF(B54=0,"NM",C54/B54-1)</f>
+        <v/>
+      </c>
+      <c r="E54" s="28">
+        <f>SUM(E44:E53)</f>
+        <v/>
+      </c>
+      <c r="F54" s="28">
+        <f>SUM(F44:F53)</f>
+        <v/>
+      </c>
+      <c r="G54" s="33">
+        <f>IF(E54=0,"NM",F54/E54-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="34" t="n"/>
+      <c r="B56" s="18" t="inlineStr">
         <is>
           <t>FY23</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C56" s="18" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="D55" s="18" t="inlineStr">
+      <c r="D56" s="18" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr">
+      <c r="E56" s="18" t="inlineStr">
         <is>
           <t>FY26</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>Solar Cells Sold, GW</t>
         </is>
       </c>
-      <c r="B56" s="19">
+      <c r="B57" s="19">
         <f>[1]DCR!AD101</f>
         <v/>
       </c>
-      <c r="C56" s="19">
+      <c r="C57" s="19">
         <f>[1]DCR!AE101</f>
         <v/>
       </c>
-      <c r="D56" s="19">
-        <f>+B53/1000</f>
-        <v/>
-      </c>
-      <c r="E56" s="19">
-        <f>+C53/1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="n"/>
-      <c r="B58" s="18" t="inlineStr">
+      <c r="D57" s="19">
+        <f>+B54/1000</f>
+        <v/>
+      </c>
+      <c r="E57" s="19">
+        <f>+C54/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="17" t="n"/>
+      <c r="B59" s="18" t="inlineStr">
         <is>
           <t>YTDFY26</t>
         </is>
       </c>
-      <c r="C58" s="18" t="inlineStr">
+      <c r="C59" s="18" t="inlineStr">
         <is>
           <t>YTDFY27</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Solar Moules Sold, GW</t>
         </is>
       </c>
-      <c r="B59" s="20">
-        <f>+E53/1000</f>
-        <v/>
-      </c>
-      <c r="C59" s="20">
-        <f>+F53/1000</f>
+      <c r="B60" s="20">
+        <f>+E54/1000</f>
+        <v/>
+      </c>
+      <c r="C60" s="20">
+        <f>+F54/1000</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B25:M25"/>
     <mergeCell ref="B3:M3"/>
-    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="N3:T3"/>
-    <mergeCell ref="N25:T25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:M26"/>
+    <mergeCell ref="N26:V26"/>
+    <mergeCell ref="N3:V3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
